--- a/data/trans_camb/P43B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P43B-Provincia-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>4,61</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 16,22</t>
+          <t>-0,29; 16,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 13,14</t>
+          <t>-2,74; 11,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 16,22</t>
+          <t>-0,29; 16,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 13,14</t>
+          <t>-2,74; 11,63</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>43,77%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 234,16</t>
+          <t>-5,93; 242,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 191,62</t>
+          <t>-18,43; 195,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 234,16</t>
+          <t>-5,93; 242,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 191,62</t>
+          <t>-18,43; 195,26</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 0,28</t>
+          <t>-12,12; 0,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 7,84</t>
+          <t>-5,76; 7,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 0,28</t>
+          <t>-12,12; 0,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 7,84</t>
+          <t>-5,76; 7,44</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 5,34</t>
+          <t>-68,5; 10,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 87,86</t>
+          <t>-31,95; 79,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 5,34</t>
+          <t>-68,5; 10,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 87,86</t>
+          <t>-31,95; 79,92</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-5,85</t>
+          <t>-5,94</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,85</t>
+          <t>-5,94</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -0,34</t>
+          <t>-16,22; -0,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 1,45</t>
+          <t>-13,15; 2,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -0,34</t>
+          <t>-16,22; -0,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 1,45</t>
+          <t>-13,15; 2,13</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-37,93%</t>
+          <t>-38,54%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-37,93%</t>
+          <t>-38,54%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,23; -1,88</t>
+          <t>-77,34; 2,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,43; 14,75</t>
+          <t>-64,88; 24,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,23; -1,88</t>
+          <t>-77,34; 2,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,43; 14,75</t>
+          <t>-64,88; 24,71</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>2,81</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,57; -1,48</t>
+          <t>-16,33; -0,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 5,91</t>
+          <t>-5,7; 10,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,57; -1,48</t>
+          <t>-16,33; -0,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 5,91</t>
+          <t>-5,7; 10,41</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-9,81%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-9,81%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,62; -7,19</t>
+          <t>-67,1; -4,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-53,39; 34,64</t>
+          <t>-22,47; 65,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,62; -7,19</t>
+          <t>-67,1; -4,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-53,39; 34,64</t>
+          <t>-22,47; 65,87</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,95</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 7,9</t>
+          <t>-8,92; 7,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 10,65</t>
+          <t>-4,01; 9,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 7,9</t>
+          <t>-8,92; 7,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 10,65</t>
+          <t>-4,01; 9,99</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-62,34; 172,73</t>
+          <t>-68,54; 161,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,76; 234,31</t>
+          <t>-29,44; 224,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,34; 172,73</t>
+          <t>-68,54; 161,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,76; 234,31</t>
+          <t>-29,44; 224,85</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>3,45</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>3,45</t>
         </is>
       </c>
     </row>
@@ -1181,22 +1181,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 9,8</t>
+          <t>-3,89; 10,06</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 8,24</t>
+          <t>-4,07; 9,56</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 9,8</t>
+          <t>-3,89; 10,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 8,24</t>
+          <t>-4,07; 9,56</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -1237,22 +1237,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-51,4; 285,11</t>
+          <t>-43,01; 356,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 251,63</t>
+          <t>-42,76; 312,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-51,4; 285,11</t>
+          <t>-43,01; 356,22</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 251,63</t>
+          <t>-42,76; 312,49</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>19,89</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>19,89</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 6,86</t>
+          <t>-5,05; 6,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 22,93</t>
+          <t>13,57; 25,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 6,86</t>
+          <t>-5,05; 6,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 22,93</t>
+          <t>13,57; 25,84</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>138,54%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>138,54%</t>
         </is>
       </c>
     </row>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 62,65</t>
+          <t>-30,72; 52,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 172,33</t>
+          <t>75,88; 230,62</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 62,65</t>
+          <t>-30,72; 52,7</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 172,33</t>
+          <t>75,88; 230,62</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-5,74</t>
+          <t>-5,9</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-5,74</t>
+          <t>-5,9</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1413,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 4,04</t>
+          <t>-7,5; 3,88</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,9; -0,18</t>
+          <t>-11,4; -0,66</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 4,04</t>
+          <t>-7,5; 3,88</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,9; -0,18</t>
+          <t>-11,4; -0,66</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-33,33%</t>
+          <t>-34,3%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-33,33%</t>
+          <t>-34,3%</t>
         </is>
       </c>
     </row>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 28,56</t>
+          <t>-35,01; 27,95</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-54,65; 0,31</t>
+          <t>-55,89; -4,13</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 28,56</t>
+          <t>-35,01; 27,95</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-54,65; 0,31</t>
+          <t>-55,89; -4,13</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>4,14</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,6</t>
+          <t>-4,43; 0,5</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 4,47</t>
+          <t>1,33; 6,55</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,6</t>
+          <t>-4,43; 0,5</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 4,47</t>
+          <t>1,33; 6,55</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -1585,22 +1585,22 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 4,37</t>
+          <t>-27,64; 4,05</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 32,78</t>
+          <t>8,11; 50,54</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 4,37</t>
+          <t>-27,64; 4,05</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 32,78</t>
+          <t>8,11; 50,54</t>
         </is>
       </c>
     </row>
